--- a/переадресація колон.xlsx
+++ b/переадресація колон.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Валерій Коростіль\OneDrive\Документи\GitHub\my\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2ID (Alena)\Documents\GitHub\my\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F395544F-2FB2-47B5-9262-C935E3369CC4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C98968-74BE-4488-97A7-741AA1134A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15150" xr2:uid="{66A218F2-A561-4DB0-9DEF-A996E84291CD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{66A218F2-A561-4DB0-9DEF-A996E84291CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>https://prolitech.com.ua/distillyatori-bitovie/tarilchasta-kolona/</t>
   </si>
@@ -38,12 +42,6 @@
     <t>https://prolitech.com.ua/ru/distillyatori-bitovie/tarilchasta-kolona/</t>
   </si>
   <si>
-    <t xml:space="preserve">OLD </t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
     <t>https://prolitech.com.ua/distillyatori-bitovie/kolpachkovaja-kolonna/</t>
   </si>
   <si>
@@ -78,16 +76,49 @@
   </si>
   <si>
     <t>https://prolitech.com.ua/ru/distillyatori-bitovie/brazhnaja-kolonna/</t>
+  </si>
+  <si>
+    <t>https://prolitech.com.ua/dla-samogonovarinna/kolony/brazhnaja-kolonna/</t>
+  </si>
+  <si>
+    <t>https://prolitech.com.ua/ru/dla-samogonovarinna/kolonny/brazhnaja-kolonna/</t>
+  </si>
+  <si>
+    <t>https://prolitech.com.ua/ru/dla-samogonovarinna/kolonny/rektifikatsionnaja-kolonna/</t>
+  </si>
+  <si>
+    <t>https://prolitech.com.ua/dla-samogonovarinna/kolony/rektifikatsionnaja-kolonna/</t>
+  </si>
+  <si>
+    <t>https://prolitech.com.ua/dla-samogonovarinna/kolony/kolpachkovaja-kolonna/</t>
+  </si>
+  <si>
+    <t>https://prolitech.com.ua/ru/dla-samogonovarinna/kolonny/kolpachkovaja-kolonna/</t>
+  </si>
+  <si>
+    <t>звідки</t>
+  </si>
+  <si>
+    <t>Куди</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -111,13 +142,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гіперпосилання" xfId="1" builtinId="8"/>
     <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -430,112 +464,151 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49222CCF-EA02-4B9B-9019-5B51458A4E28}">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="7.28515625" customWidth="1"/>
     <col min="3" max="3" width="70.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.28515625" customWidth="1"/>
+    <col min="4" max="4" width="82.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="D7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C7" r:id="rId1" xr:uid="{FA796353-EBB9-47D3-98A8-1EF34A541CF9}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{44542BCF-24DE-4CF3-BF17-0932ED252711}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{9DEAB141-205A-40FD-B9CD-7B4CE138DF2E}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{360823A6-4235-4F95-B8D5-DD1437F0DCE4}"/>
+    <hyperlink ref="C3" r:id="rId5" xr:uid="{F95F2204-66B8-499A-9B30-0F9D912C80E4}"/>
+    <hyperlink ref="C2" r:id="rId6" xr:uid="{B281E5FE-73BF-4BDE-9725-E6356B97F0FB}"/>
+    <hyperlink ref="C5" r:id="rId7" xr:uid="{6BCD3640-68A3-41A4-972B-D26B0F8FD844}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>